--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-31).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-31).xlsx
@@ -935,10 +935,10 @@
     <t>214</t>
   </si>
   <si>
-    <t>21</t>
+    <t>20</t>
   </si>
   <si>
-    <t>R$ 3.297,85</t>
+    <t>R$ 3.298,55</t>
   </si>
   <si>
     <t>36.8</t>
@@ -947,7 +947,7 @@
     <t>23.3</t>
   </si>
   <si>
-    <t>4.86</t>
+    <t>4.87</t>
   </si>
   <si>
     <t>19.2</t>
@@ -959,7 +959,7 @@
     <t>6.5</t>
   </si>
   <si>
-    <t>44.0%</t>
+    <t>44.2%</t>
   </si>
   <si>
     <t>19.3%</t>
@@ -10181,7 +10181,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10211,18 +10211,30 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
+      <c r="M58" s="5">
+        <v>3433.1300000000001</v>
+      </c>
+      <c r="N58" s="6">
+        <v>39</v>
+      </c>
       <c r="O58" s="6">
         <v>31</v>
       </c>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
+      <c r="P58" s="7">
+        <v>5.0223684210526311</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>17.240861290322577</v>
+      </c>
+      <c r="R58" s="8">
+        <v>5.3394433333333335</v>
+      </c>
       <c r="S58" s="8">
         <v>7</v>
       </c>
-      <c r="T58" s="9"/>
+      <c r="T58" s="9">
+        <v>0.29032258064516131</v>
+      </c>
       <c r="U58" s="9">
         <v>0.064516129032258063</v>
       </c>
